--- a/data/trans_dic/IP11-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han sufrido algún accidente por el cual necesitase asiscencia sanitaria en los últimos 12 meses.</t>
+          <t>Menores que han sufrido algún accidente por el cual necesitase asiscencia sanitaria en los últimos 12 meses. (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,34</t>
+          <t>1,2; 7,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 11,39</t>
+          <t>4,05; 11,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,38</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,63</t>
+          <t>0,0; 4,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 10,12</t>
+          <t>3,12; 9,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 10,71</t>
+          <t>3,69; 10,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,15</t>
+          <t>0,57; 4,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,76</t>
+          <t>0,0; 6,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,05</t>
+          <t>2,73; 7,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,39</t>
+          <t>4,64; 9,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,09</t>
+          <t>0,66; 3,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,38</t>
+          <t>0,6; 4,5</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,75</t>
+          <t>3,41; 8,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 11,22</t>
+          <t>5,5; 11,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,61</t>
+          <t>1,51; 5,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,98</t>
+          <t>0,91; 5,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 9,12</t>
+          <t>3,92; 9,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 14,07</t>
+          <t>7,34; 13,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 6,99</t>
+          <t>2,62; 6,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,02</t>
+          <t>1,22; 6,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,62</t>
+          <t>4,22; 7,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,18; 11,48</t>
+          <t>7,43; 11,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,36</t>
+          <t>2,49; 5,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,84</t>
+          <t>1,48; 4,52</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 10,77</t>
+          <t>3,63; 11,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 10,96</t>
+          <t>4,04; 11,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,91</t>
+          <t>1,66; 5,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 5,47</t>
+          <t>1,26; 5,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 12,05</t>
+          <t>4,81; 11,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 12,52</t>
+          <t>4,79; 12,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 10,02</t>
+          <t>3,9; 10,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 7,12</t>
+          <t>1,65; 7,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 10,47</t>
+          <t>4,8; 9,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,25; 10,39</t>
+          <t>5,31; 10,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 6,98</t>
+          <t>3,3; 7,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,51</t>
+          <t>1,97; 5,35</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,98</t>
+          <t>2,91; 8,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,65</t>
+          <t>3,97; 10,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,46</t>
+          <t>3,1; 8,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,89</t>
+          <t>1,42; 5,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 9,29</t>
+          <t>3,72; 9,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,33; 17,35</t>
+          <t>9,65; 17,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 12,07</t>
+          <t>5,23; 12,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,36</t>
+          <t>1,6; 5,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,48</t>
+          <t>3,96; 7,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,58; 12,97</t>
+          <t>7,77; 13,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 9,46</t>
+          <t>4,78; 9,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,56</t>
+          <t>1,87; 4,47</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,65</t>
+          <t>3,99; 6,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 8,93</t>
+          <t>5,82; 8,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,48</t>
+          <t>2,42; 4,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,81</t>
+          <t>1,61; 3,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,09</t>
+          <t>5,1; 8,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,14; 11,67</t>
+          <t>8,08; 11,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,04</t>
+          <t>4,21; 7,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,62</t>
+          <t>2,17; 4,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,98; 6,9</t>
+          <t>4,91; 6,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 9,83</t>
+          <t>7,37; 9,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,45</t>
+          <t>3,62; 5,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,83</t>
+          <t>2,14; 3,74</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han sufrido algún accidente por el cual necesitase asiscencia sanitaria en los últimos 12 meses. (tasa de respuesta: 99,87%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10712</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7037</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1337</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>10565</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19922</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3858</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1271; 7480</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5931; 16469</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3917</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2555</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3791; 11975</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5319; 15692</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>704; 6143</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4179</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>6201; 16241</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>13472; 27182</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1685; 8102</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>708; 5339</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>13363</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18470</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6346</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3718</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16060</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>28238</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11379</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5558</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>29423</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>46707</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>17724</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>9276</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>8634; 20827</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13001; 26659</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3161; 11412</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1457; 8081</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9944; 22924</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>19732; 36912</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>6738; 17680</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2228; 11094</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>21415; 38592</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>37527; 59829</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>11648; 24893</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5048; 15445</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8794</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10777</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6265</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4878</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>11060</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12458</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12191</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>7702</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>19854</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>23234</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>18456</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>12581</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4634; 14747</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6344; 17483</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3134; 10904</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2187; 10385</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6804; 16810</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7560; 19552</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7355; 18899</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3494; 15209</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>12918; 26855</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>16741; 32718</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>12460; 26818</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>7591; 20610</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>9618</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11754</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9639</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7797</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12369</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23472</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>14415</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>9436</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>21987</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>35226</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>24054</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>17233</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>5654; 15724</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6810; 17847</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5337; 15146</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3921; 13823</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>7673; 18728</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>17374; 31819</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>9071; 21118</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>4890; 16603</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>15834; 30936</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>27304; 45684</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>16518; 32742</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>10868; 25958</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>35304</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>51712</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>23369</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>17151</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>24034</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>81829</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>125089</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>64093</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>41185</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>27177; 45823</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>41383; 63152</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>16956; 32398</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10722; 24148</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>36857; 57878</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>60681; 88164</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>31315; 52415</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>16495; 34648</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>68914; 97386</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>107822; 143696</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>52335; 77356</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>30595; 53334</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,04</t>
+          <t>1,14; 6,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 11,25</t>
+          <t>4,32; 11,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,48</t>
+          <t>0,0; 4,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,87</t>
+          <t>3,15; 9,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 10,89</t>
+          <t>3,61; 10,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,95</t>
+          <t>0,59; 5,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,8</t>
+          <t>0,0; 8,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,14</t>
+          <t>2,78; 7,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 9,36</t>
+          <t>4,66; 9,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,17</t>
+          <t>0,54; 3,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,5</t>
+          <t>0,53; 4,35</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 8,23</t>
+          <t>3,32; 7,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 11,28</t>
+          <t>5,21; 11,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,44</t>
+          <t>1,44; 5,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,07</t>
+          <t>0,92; 4,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 9,03</t>
+          <t>4,23; 9,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 13,72</t>
+          <t>7,53; 13,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,87</t>
+          <t>2,67; 7,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,08</t>
+          <t>1,3; 6,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 7,61</t>
+          <t>4,24; 7,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 11,84</t>
+          <t>7,28; 11,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,33</t>
+          <t>2,63; 5,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,52</t>
+          <t>1,48; 4,66</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 11,56</t>
+          <t>3,82; 11,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 11,13</t>
+          <t>4,09; 11,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,77</t>
+          <t>1,66; 5,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,97</t>
+          <t>1,01; 5,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 11,88</t>
+          <t>4,46; 12,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 12,38</t>
+          <t>4,51; 12,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 10,02</t>
+          <t>3,77; 9,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,19</t>
+          <t>1,68; 7,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 9,98</t>
+          <t>5,06; 10,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,31; 10,39</t>
+          <t>5,11; 10,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 7,1</t>
+          <t>3,43; 7,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,35</t>
+          <t>1,94; 5,09</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,1</t>
+          <t>2,91; 8,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 10,42</t>
+          <t>4,27; 10,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 8,81</t>
+          <t>3,47; 9,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,02</t>
+          <t>1,32; 4,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 9,09</t>
+          <t>3,9; 9,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,65; 17,68</t>
+          <t>9,28; 17,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 12,18</t>
+          <t>5,18; 12,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,44</t>
+          <t>1,62; 5,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 7,73</t>
+          <t>3,83; 7,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,77; 13,0</t>
+          <t>7,71; 12,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 9,48</t>
+          <t>4,9; 9,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,47</t>
+          <t>1,98; 4,61</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,73</t>
+          <t>3,85; 6,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,88</t>
+          <t>5,71; 9,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,61</t>
+          <t>2,45; 4,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,63</t>
+          <t>1,6; 3,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 8,01</t>
+          <t>5,07; 8,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,08; 11,74</t>
+          <t>8,06; 11,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,05</t>
+          <t>4,22; 7,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,55</t>
+          <t>2,15; 4,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,94</t>
+          <t>4,92; 6,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,83</t>
+          <t>7,43; 9,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 5,35</t>
+          <t>3,65; 5,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,74</t>
+          <t>2,1; 3,69</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1271; 7480</t>
+          <t>1206; 7369</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5931; 16469</t>
+          <t>6319; 16387</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3917</t>
+          <t>0; 3380</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2555</t>
+          <t>0; 2585</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3791; 11975</t>
+          <t>3829; 11997</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5319; 15692</t>
+          <t>5208; 14779</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>704; 6143</t>
+          <t>735; 6799</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4179</t>
+          <t>0; 5507</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6201; 16241</t>
+          <t>6324; 16047</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13472; 27182</t>
+          <t>13541; 27711</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1685; 8102</t>
+          <t>1389; 8255</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>708; 5339</t>
+          <t>628; 5161</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8634; 20827</t>
+          <t>8396; 19721</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13001; 26659</t>
+          <t>12299; 26864</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3161; 11412</t>
+          <t>3012; 10974</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1457; 8081</t>
+          <t>1472; 7901</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9944; 22924</t>
+          <t>10742; 23112</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19732; 36912</t>
+          <t>20267; 37277</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6738; 17680</t>
+          <t>6868; 18266</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2228; 11094</t>
+          <t>2367; 11150</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21415; 38592</t>
+          <t>21509; 38298</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37527; 59829</t>
+          <t>36776; 57764</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11648; 24893</t>
+          <t>12269; 26172</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5048; 15445</t>
+          <t>5061; 15920</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4634; 14747</t>
+          <t>4869; 14855</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6344; 17483</t>
+          <t>6424; 17608</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3134; 10904</t>
+          <t>3141; 11057</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2187; 10385</t>
+          <t>1745; 10071</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6804; 16810</t>
+          <t>6317; 17600</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7560; 19552</t>
+          <t>7127; 19721</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7355; 18899</t>
+          <t>7107; 18686</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3494; 15209</t>
+          <t>3550; 15087</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12918; 26855</t>
+          <t>13611; 27986</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16741; 32718</t>
+          <t>16091; 31713</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12460; 26818</t>
+          <t>12956; 27060</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7591; 20610</t>
+          <t>7456; 19571</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5654; 15724</t>
+          <t>5644; 15544</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6810; 17847</t>
+          <t>7323; 18767</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5337; 15146</t>
+          <t>5971; 15747</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3921; 13823</t>
+          <t>3627; 13526</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7673; 18728</t>
+          <t>8042; 18651</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17374; 31819</t>
+          <t>16704; 31367</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9071; 21118</t>
+          <t>8987; 20970</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4890; 16603</t>
+          <t>4942; 16599</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15834; 30936</t>
+          <t>15345; 30667</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27304; 45684</t>
+          <t>27101; 45251</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16518; 32742</t>
+          <t>16912; 33461</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10868; 25958</t>
+          <t>11504; 26775</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>27177; 45823</t>
+          <t>26187; 45694</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>41383; 63152</t>
+          <t>40579; 65077</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16956; 32398</t>
+          <t>17224; 31776</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10722; 24148</t>
+          <t>10652; 25105</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>36857; 57878</t>
+          <t>36605; 58829</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60681; 88164</t>
+          <t>60540; 87567</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31315; 52415</t>
+          <t>31377; 52052</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16495; 34648</t>
+          <t>16368; 35058</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>68914; 97386</t>
+          <t>69001; 96090</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>107822; 143696</t>
+          <t>108681; 142229</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52335; 77356</t>
+          <t>52697; 76910</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30595; 53334</t>
+          <t>29937; 52614</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3,32%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7,32%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,94</t>
+          <t>3,18; 10,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 11,2</t>
+          <t>3,95; 10,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,53; 5,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,53</t>
+          <t>0,0; 7,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 9,88</t>
+          <t>1,21; 7,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 10,25</t>
+          <t>4,47; 11,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,48</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,96</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,05</t>
+          <t>2,77; 7,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 9,54</t>
+          <t>4,74; 9,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,23</t>
+          <t>0,5; 3,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,35</t>
+          <t>0,54; 4,49</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,28%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,82%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>3,03%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,32; 7,79</t>
+          <t>4,09; 9,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 11,37</t>
+          <t>7,79; 14,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,24</t>
+          <t>2,78; 6,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,96</t>
+          <t>1,23; 5,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 9,11</t>
+          <t>3,25; 7,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,53; 13,86</t>
+          <t>5,27; 11,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,1</t>
+          <t>1,38; 5,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,11</t>
+          <t>0,97; 5,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,55</t>
+          <t>4,32; 7,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,28; 11,43</t>
+          <t>7,18; 11,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,6</t>
+          <t>2,61; 5,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,66</t>
+          <t>1,41; 4,91</t>
         </is>
       </c>
     </row>
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,82%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,89%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6,86%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,32%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>7,38%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 11,65</t>
+          <t>4,55; 12,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,09; 11,21</t>
+          <t>4,61; 12,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,85</t>
+          <t>3,99; 10,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,82</t>
+          <t>1,68; 7,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 12,44</t>
+          <t>3,81; 10,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 12,48</t>
+          <t>4,21; 10,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 9,91</t>
+          <t>1,46; 5,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 7,14</t>
+          <t>1,1; 5,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 10,4</t>
+          <t>5,09; 10,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 10,07</t>
+          <t>5,25; 10,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,43; 7,17</t>
+          <t>3,26; 6,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,09</t>
+          <t>1,9; 5,59</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,04%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8,31%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4,96%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,86%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,61%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,01</t>
+          <t>3,66; 9,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,27; 10,95</t>
+          <t>9,33; 17,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 9,16</t>
+          <t>5,16; 12,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,91</t>
+          <t>1,37; 5,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 9,05</t>
+          <t>2,86; 7,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,28; 17,43</t>
+          <t>4,26; 10,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 12,09</t>
+          <t>3,36; 9,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,43</t>
+          <t>1,52; 5,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,66</t>
+          <t>3,94; 7,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,71; 12,88</t>
+          <t>7,58; 12,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 9,69</t>
+          <t>4,83; 9,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,61</t>
+          <t>1,97; 4,57</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>5,18%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>7,27%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,33%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,71</t>
+          <t>5,08; 8,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 9,15</t>
+          <t>8,14; 11,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,53</t>
+          <t>4,12; 7,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,78</t>
+          <t>2,14; 4,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,14</t>
+          <t>3,85; 6,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,06; 11,66</t>
+          <t>5,81; 8,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,22; 7,0</t>
+          <t>2,3; 4,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,61</t>
+          <t>1,89; 4,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,85</t>
+          <t>4,98; 6,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 9,73</t>
+          <t>7,41; 9,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 5,32</t>
+          <t>3,64; 5,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,69</t>
+          <t>2,24; 3,81</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,37 +1509,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7037</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1191</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3529</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>10712</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1119</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>758</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7037</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9210</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2739</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>566</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>1757</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1206; 7369</t>
+          <t>3856; 12288</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6319; 16387</t>
+          <t>5699; 15435</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3380</t>
+          <t>652; 6399</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2585</t>
+          <t>0; 3664</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3829; 11997</t>
+          <t>1286; 7791</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5208; 14779</t>
+          <t>6547; 16663</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>735; 6799</t>
+          <t>0; 4455</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5507</t>
+          <t>0; 2013</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6324; 16047</t>
+          <t>6301; 16045</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13541; 27711</t>
+          <t>13781; 27266</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1389; 8255</t>
+          <t>1280; 7894</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>628; 5161</t>
+          <t>552; 4593</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16060</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28238</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11379</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4702</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>13363</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>18470</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6346</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3718</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16060</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28238</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11379</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>8329</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8396; 19721</t>
+          <t>10391; 23141</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12299; 26864</t>
+          <t>20944; 37850</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3012; 10974</t>
+          <t>7162; 17983</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1472; 7901</t>
+          <t>1941; 9415</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10742; 23112</t>
+          <t>8224; 19622</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20267; 37277</t>
+          <t>12457; 26503</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6868; 18266</t>
+          <t>2893; 11760</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2367; 11150</t>
+          <t>1408; 7820</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21509; 38298</t>
+          <t>21895; 38639</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36776; 57764</t>
+          <t>36266; 58019</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12269; 26172</t>
+          <t>12193; 25034</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5061; 15920</t>
+          <t>4286; 14890</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>11060</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12458</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12191</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7522</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>8794</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>10777</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>6265</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4878</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>11060</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12458</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12191</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>12444</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4869; 14855</t>
+          <t>6433; 17060</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6424; 17608</t>
+          <t>7288; 19774</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3141; 11057</t>
+          <t>7529; 18898</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1745; 10071</t>
+          <t>3350; 14613</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6317; 17600</t>
+          <t>4860; 13741</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7127; 19721</t>
+          <t>6609; 17210</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7107; 18686</t>
+          <t>2754; 11167</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3550; 15087</t>
+          <t>1916; 9516</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13611; 27986</t>
+          <t>13684; 28174</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16091; 31713</t>
+          <t>16543; 32728</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12956; 27060</t>
+          <t>12308; 26332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7456; 19571</t>
+          <t>7100; 20881</t>
         </is>
       </c>
     </row>
@@ -2133,37 +2133,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12369</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23472</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14415</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8836</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>9618</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>11754</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>9639</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7797</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12369</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23472</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14415</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17233</t>
+          <t>16905</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5644; 15544</t>
+          <t>7551; 19148</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7323; 18767</t>
+          <t>16783; 31214</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5971; 15747</t>
+          <t>8948; 20922</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3627; 13526</t>
+          <t>4000; 15437</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8042; 18651</t>
+          <t>5545; 15480</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16704; 31367</t>
+          <t>7298; 18248</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8987; 20970</t>
+          <t>5779; 16257</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4942; 16599</t>
+          <t>3891; 13224</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15345; 30667</t>
+          <t>15752; 29945</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27101; 45251</t>
+          <t>26634; 45559</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16912; 33461</t>
+          <t>16667; 32654</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11504; 26775</t>
+          <t>10833; 25102</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>35304</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>51712</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26187; 45694</t>
+          <t>36682; 58494</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>40579; 65077</t>
+          <t>61136; 87643</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17224; 31776</t>
+          <t>30622; 52365</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10652; 25105</t>
+          <t>14992; 32709</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>36605; 58829</t>
+          <t>26221; 45310</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60540; 87567</t>
+          <t>41292; 63464</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31377; 52052</t>
+          <t>16176; 31456</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16368; 35058</t>
+          <t>11864; 25644</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>69001; 96090</t>
+          <t>69862; 96898</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>108681; 142229</t>
+          <t>108382; 143766</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52697; 76910</t>
+          <t>52656; 78791</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29937; 52614</t>
+          <t>29723; 50648</t>
         </is>
       </c>
     </row>
